--- a/utils/TestData.xlsx
+++ b/utils/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varam/Desktop/NumpyNinja/Cucumber_SuiteCRM/utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48453F64-A06E-2F40-A39E-150499D67903}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D61CD2-BBDF-E448-A6C8-AFAB66A79FEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10100" yWindow="660" windowWidth="18620" windowHeight="16660" activeTab="2" xr2:uid="{81BEAC59-F4C8-E544-AECB-0A731E05AD51}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28720" windowHeight="16660" activeTab="2" xr2:uid="{81BEAC59-F4C8-E544-AECB-0A731E05AD51}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="109">
   <si>
     <t>username</t>
   </si>
@@ -281,9 +281,6 @@
     <t>CA</t>
   </si>
   <si>
-    <t>Dummy account...</t>
-  </si>
-  <si>
     <t>Acme Technologies</t>
   </si>
   <si>
@@ -302,9 +299,6 @@
     <t>NY</t>
   </si>
   <si>
-    <t>Test account...</t>
-  </si>
-  <si>
     <t>Sunrise Healthcare</t>
   </si>
   <si>
@@ -318,6 +312,48 @@
   </si>
   <si>
     <t>San Francisco</t>
+  </si>
+  <si>
+    <t>billingStreet</t>
+  </si>
+  <si>
+    <t>billingPostalcode</t>
+  </si>
+  <si>
+    <t>shippingStreet</t>
+  </si>
+  <si>
+    <t>shippingPostalcode</t>
+  </si>
+  <si>
+    <t>shippingState</t>
+  </si>
+  <si>
+    <t>shippingCountry</t>
+  </si>
+  <si>
+    <t>25 King Street</t>
+  </si>
+  <si>
+    <t>Dummy account for B.C. Investing International</t>
+  </si>
+  <si>
+    <t>100 Market Street</t>
+  </si>
+  <si>
+    <t>200 Park Avenue</t>
+  </si>
+  <si>
+    <t>Test account for Acme Technologies</t>
+  </si>
+  <si>
+    <t>450 Mission Street</t>
+  </si>
+  <si>
+    <t>500 Howard Street</t>
+  </si>
+  <si>
+    <t>Test account for Sunrise Healthcare</t>
   </si>
 </sst>
 </file>
@@ -1051,15 +1087,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948EB979-9CC2-254F-8D80-42EBE580ACF4}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,22 +1113,40 @@
         <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1108,93 +1163,147 @@
         <v>81</v>
       </c>
       <c r="F2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2">
+        <v>59018</v>
+      </c>
+      <c r="H2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>66</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2">
+        <v>59018</v>
+      </c>
+      <c r="M2" t="s">
         <v>82</v>
       </c>
-      <c r="J2" t="s">
-        <v>84</v>
+      <c r="N2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>70</v>
       </c>
       <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
         <v>86</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3">
+        <v>10001</v>
+      </c>
+      <c r="H3" t="s">
         <v>88</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" t="s">
-        <v>66</v>
       </c>
       <c r="I3" t="s">
         <v>89</v>
       </c>
       <c r="J3" t="s">
-        <v>91</v>
+        <v>66</v>
+      </c>
+      <c r="K3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3">
+        <v>10017</v>
+      </c>
+      <c r="M3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>71</v>
       </c>
       <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4">
+        <v>94105</v>
+      </c>
+      <c r="H4" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>83</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>66</v>
       </c>
-      <c r="I4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" t="s">
-        <v>91</v>
+      <c r="K4" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4">
+        <v>94105</v>
+      </c>
+      <c r="M4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://www.hrinvo.us/" xr:uid="{8A9AA5A7-77C3-A94E-A2A9-59C33AC9B3B6}"/>
-    <hyperlink ref="E2" r:id="rId2" display="mailto:qa94@example.info" xr:uid="{218532AC-549A-054E-9E5C-C382EFEA0B5B}"/>
-    <hyperlink ref="C3" r:id="rId3" display="https://www.acmetech.example/" xr:uid="{4D164C7F-2C9C-0F40-BCF5-299655225C3B}"/>
-    <hyperlink ref="E3" r:id="rId4" display="mailto:contact@acmetech.example" xr:uid="{5E6D0A43-B6D0-684E-ABD2-25D69753B7A3}"/>
-    <hyperlink ref="C4" r:id="rId5" display="https://www.sunrisehealth.example/" xr:uid="{1A2B6CBB-E042-1442-A6EB-8BD9EB80B2B0}"/>
-    <hyperlink ref="E4" r:id="rId6" display="mailto:info@sunrisehealth.example" xr:uid="{DE64D143-762C-F246-8EBA-11F75DA20A67}"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://www.hrinvo.us/" xr:uid="{15CD0DD6-8F30-4F48-A00C-CD2294F6882A}"/>
+    <hyperlink ref="E2" r:id="rId2" display="mailto:qa94@example.info" xr:uid="{5EDCE3E4-7C3E-DB44-9C53-019C4C14592D}"/>
+    <hyperlink ref="C3" r:id="rId3" display="https://www.acmetech.example/" xr:uid="{5FF8E648-FEBA-8743-99FE-B4C212D52ADB}"/>
+    <hyperlink ref="E3" r:id="rId4" display="mailto:contact@acmetech.example" xr:uid="{E8F2B0CC-7606-3044-BB22-F814FDA7392D}"/>
+    <hyperlink ref="C4" r:id="rId5" display="https://www.sunrisehealth.example/" xr:uid="{91E4C37E-E4DA-3241-BC31-7EAF44273014}"/>
+    <hyperlink ref="E4" r:id="rId6" display="mailto:info@sunrisehealth.example" xr:uid="{4FBF416C-E6D7-864E-9CE2-B635267B5F3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
